--- a/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -30,13 +30,13 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.0.1</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>CS_RuimPropertyCodes</t>
+    <t>CSRuimPropertyCodes</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T13:07:32+00:00</t>
+    <t>2026-03-30T14:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T14:08:45+00:00</t>
+    <t>2026-03-30T14:14:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T14:14:17+00:00</t>
+    <t>2026-03-30T14:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T14:14:21+00:00</t>
+    <t>2026-03-30T14:30:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T14:30:44+00:00</t>
+    <t>2026-03-30T14:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T14:30:53+00:00</t>
+    <t>2026-03-30T15:16:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/main/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:16:42+00:00</t>
+    <t>2026-06-26T11:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
